--- a/ampex-d175-terminal/digital-to-crt-pinout-and-components.xlsx
+++ b/ampex-d175-terminal/digital-to-crt-pinout-and-components.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matt\Dropbox\Projects\serial-terminals\ampex-d175-terminal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9BAC2F-32E9-4E55-80F9-6DDF037217AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844224CA-EB15-4C43-9D7C-C71BC125D7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="video_timing" sheetId="2" r:id="rId2"/>
-    <sheet name="video_2" sheetId="3" r:id="rId3"/>
+    <sheet name="components" sheetId="1" r:id="rId1"/>
+    <sheet name="video_timing" sheetId="3" r:id="rId2"/>
+    <sheet name="video_timing_misc" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="146">
   <si>
     <t>Pin</t>
   </si>
@@ -121,9 +121,6 @@
     <t>Unreg V+ 10.9V</t>
   </si>
   <si>
-    <t>12v rail caps</t>
-  </si>
-  <si>
     <t>C110</t>
   </si>
   <si>
@@ -157,45 +154,6 @@
     <t>10000uf 25v</t>
   </si>
   <si>
-    <t>Pre-fix:</t>
-  </si>
-  <si>
-    <t>5v rail</t>
-  </si>
-  <si>
-    <t>pre-reg 5v @ C107</t>
-  </si>
-  <si>
-    <t>~ 120hz, 0.77 ripple, 10.9v</t>
-  </si>
-  <si>
-    <t>66 mV ripple, 5.02v</t>
-  </si>
-  <si>
-    <t>12v rail</t>
-  </si>
-  <si>
-    <t>pre-reg 12v @ C108</t>
-  </si>
-  <si>
-    <t>~ 120hz, 1.6v ripple, 21.4v</t>
-  </si>
-  <si>
-    <t>191 mV ripple, 11.85v</t>
-  </si>
-  <si>
-    <t>Full screen</t>
-  </si>
-  <si>
-    <t>1.9 V</t>
-  </si>
-  <si>
-    <t>235 mV</t>
-  </si>
-  <si>
-    <t>~ 0.5v when looked at 20 us/div</t>
-  </si>
-  <si>
     <t>C501</t>
   </si>
   <si>
@@ -247,9 +205,6 @@
     <t>C205</t>
   </si>
   <si>
-    <t>25uF 25v non-polar ?</t>
-  </si>
-  <si>
     <t>C503</t>
   </si>
   <si>
@@ -373,9 +328,6 @@
     <t>us</t>
   </si>
   <si>
-    <t>Line</t>
-  </si>
-  <si>
     <t>VFP</t>
   </si>
   <si>
@@ -437,6 +389,93 @@
   </si>
   <si>
     <t>By LM556 U3, right side timer (pins 8-13)</t>
+  </si>
+  <si>
+    <t>12v rail cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25uF 25v non-polar </t>
+  </si>
+  <si>
+    <t>U101</t>
+  </si>
+  <si>
+    <t>U102</t>
+  </si>
+  <si>
+    <t>U301</t>
+  </si>
+  <si>
+    <t>Q201</t>
+  </si>
+  <si>
+    <t>Q202</t>
+  </si>
+  <si>
+    <t>Q401</t>
+  </si>
+  <si>
+    <t>T202</t>
+  </si>
+  <si>
+    <t>NS401</t>
+  </si>
+  <si>
+    <t>NS501</t>
+  </si>
+  <si>
+    <t>Horiz 1</t>
+  </si>
+  <si>
+    <t>Horiz 2</t>
+  </si>
+  <si>
+    <t>MJ9434   NPN</t>
+  </si>
+  <si>
+    <t>2N2896</t>
+  </si>
+  <si>
+    <t>BU407</t>
+  </si>
+  <si>
+    <t>NEC uPC1031H2</t>
+  </si>
+  <si>
+    <t>MC7812CT</t>
+  </si>
+  <si>
+    <t>LM323K</t>
+  </si>
+  <si>
+    <t>HSIN LING 3512880-01</t>
+  </si>
+  <si>
+    <t>NEON BULB</t>
+  </si>
+  <si>
+    <t>Chars</t>
+  </si>
+  <si>
+    <t>80 x 25</t>
+  </si>
+  <si>
+    <t>Resolution</t>
+  </si>
+  <si>
+    <t>560 x 300</t>
+  </si>
+  <si>
+    <t>Total lines</t>
+  </si>
+  <si>
+    <t>Line tot</t>
+  </si>
+  <si>
+    <t>Pix</t>
+  </si>
+  <si>
+    <t>Total V Blanking</t>
   </si>
 </sst>
 </file>
@@ -498,16 +537,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,6 +563,72 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E478954E-C0C9-1D6C-D2E5-D4CC5550CD24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5276850" y="1714500"/>
+          <a:ext cx="5048250" cy="2809875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1447,11 +1550,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1598,208 +1701,651 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>33</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>27</v>
+        <v>55</v>
+      </c>
+      <c r="C28" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="C33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="C36" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" t="s">
-        <v>46</v>
-      </c>
-      <c r="E39" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" t="s">
-        <v>50</v>
-      </c>
-      <c r="F40" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:F28">
+    <sortCondition ref="B13:B28"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29136BB5-95B3-4C7C-B5A9-46E65D959436}">
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2">
+        <v>2.1055000000000001</v>
+      </c>
+      <c r="C2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="E2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3">
+        <v>14.736000000000001</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14">
+        <f>B14*7</f>
+        <v>560</v>
+      </c>
+      <c r="E14" t="s">
+        <v>144</v>
+      </c>
+      <c r="F14">
+        <f>B14*0.475</f>
+        <v>38</v>
+      </c>
+      <c r="G14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:D18" si="0">B15*7</f>
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>144</v>
+      </c>
+      <c r="F15">
+        <f t="shared" ref="F15:F18" si="1">B15*0.475</f>
+        <v>0.95</v>
+      </c>
+      <c r="G15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>3.8</v>
+      </c>
+      <c r="G16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>112</v>
+      </c>
+      <c r="E17" t="s">
+        <v>144</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>7.6</v>
+      </c>
+      <c r="G17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18">
+        <v>106</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>742</v>
+      </c>
+      <c r="E18" t="s">
+        <v>144</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>50.349999999999994</v>
+      </c>
+      <c r="G18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20">
+        <f>B20*D$18</f>
+        <v>5936</v>
+      </c>
+      <c r="E20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F20">
+        <f>D20*0.067857</f>
+        <v>402.79915199999999</v>
+      </c>
+      <c r="G20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21">
+        <f t="shared" ref="D21:D23" si="2">B21*D$18</f>
+        <v>2226</v>
+      </c>
+      <c r="E21" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21">
+        <f t="shared" ref="F21:F23" si="3">D21*0.067857</f>
+        <v>151.04968199999999</v>
+      </c>
+      <c r="G21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="2"/>
+        <v>14840</v>
+      </c>
+      <c r="E22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="3"/>
+        <v>1006.99788</v>
+      </c>
+      <c r="G22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23">
+        <f>SUM(B20:B22)</f>
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="2"/>
+        <v>23002</v>
+      </c>
+      <c r="E23" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="3"/>
+        <v>1560.846714</v>
+      </c>
+      <c r="G23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A832471-060A-4267-93BC-0B25B8865F33}">
   <dimension ref="A1:Z171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1812,27 +2358,27 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B2">
         <v>19872</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D2">
         <v>15.945</v>
@@ -1843,10 +2389,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D3">
         <v>3.8</v>
@@ -1859,401 +2405,152 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="B4">
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="J4" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="A11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="A12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
     </row>
     <row r="20" spans="16:16" x14ac:dyDescent="0.25">
       <c r="P20" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="16:16" x14ac:dyDescent="0.25">
       <c r="P21" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="26:26" x14ac:dyDescent="0.25">
       <c r="Z45" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G56" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="7:15" x14ac:dyDescent="0.25">
       <c r="O59" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="7:15" x14ac:dyDescent="0.25">
       <c r="O60" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R72" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29136BB5-95B3-4C7C-B5A9-46E65D959436}">
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="3">
-        <v>2.1055000000000001</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" s="3">
-        <v>14.736000000000001</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B14">
-        <v>106</v>
-      </c>
-      <c r="C14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B16">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17">
-        <v>3</v>
-      </c>
-      <c r="C17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>113</v>
-      </c>
-      <c r="B18">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>